--- a/data/processed/ontology/enterprise/predicate_lexicon.xlsx
+++ b/data/processed/ontology/enterprise/predicate_lexicon.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2959,27 +2959,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PRED_CAP_LAI_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP_VA_CAP_</t>
+          <t>PRED_XEM_XET_VA_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>cấp lại Giấy chứng nhận đăng ký doanh nghiệp và cập nhật tình trạng pháp lý của công ty trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp.</t>
+          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cấp lại Giấy chứng nhận đăng ký doanh nghiệp và cập nhật tình trạng pháp lý của công ty trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. | cấp lại Giấy chứng nhận đăng ký doanh nghiệp và cập nhật tình trạng pháp lý của công ty trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. với cơ quan đăng ký kinh doanh</t>
+          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp | xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>tham_dinh_ho_so</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>cap_lai_giay_chung_nhan_dang_ky_doanh_nghiep_va_cap_nhat_tinh_trang_phap_ly_cua_cong_ty_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3024,39 +3024,39 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_lai_giay_chung_nhan_dang_ky_doanh_nghiep_va_cap_nhat_tinh_trang_phap_ly_cua_cong_ty_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PRED_XEM_XET_VA_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_NEU_CO_DU_DIEU_KIEN_QUY_DINH_TAI_KHOAN_1_DIEU_NAY_VA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp | xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tham_dinh_ho_so</t>
+          <t>dieu_kien_ap_dung</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>dieu_kien</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
+          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp.</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. với cơ quan đăng ký kinh doanh</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3175,32 +3175,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PRED_NEU_CO_DU_DIEU_KIEN_QUY_DINH_TAI_KHOAN_1_DIEU_NAY_VA</t>
+          <t>PRED_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về với cơ quan đăng ký kinh doanh</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp | Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
+          <t>giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3235,61 +3235,61 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_giay_chung_nhan_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PRED_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_THONG_BAO_BANG_VAN_BAN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp | Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh | thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>thong_bao_bang_van_ban</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>chậm nhất là 03 ngày làm việc trước ngày tạm ngừng kinh doanh hoặc tiếp tục kinh doanh trước thời hạn đã thông báo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>co</t>
@@ -3312,49 +3312,49 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_giay_chung_nhan_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_thong_bao_bang_van_ban;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PRED_THONG_BAO_BANG_VAN_BAN</t>
+          <t>PRED_GUI_HO_SO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh</t>
+          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh | thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
+          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh | gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>thong_bao_bang_van_ban</t>
+          <t>gui_ho_so</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>chậm nhất là 03 ngày làm việc trước ngày tạm ngừng kinh doanh hoặc tiếp tục kinh doanh trước thời hạn đã thông báo</t>
+          <t>thời hạn</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3384,59 +3384,55 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thong_bao_bang_van_ban;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_gui_ho_so;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PRED_GUI_HO_SO</t>
+          <t>PRED_THU_HOI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh | gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>gui_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>thời hạn</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3456,39 +3452,39 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_ho_so;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_thu_hoi</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PRED_THU_HOI</t>
+          <t>PRED_CAP_DANG_KY_CO_TRACH_NHIEM_TICH_HOP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
+          <t>cấp đăng ký có trách nhiệm tích hợp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
+          <t>cấp đăng ký có trách nhiệm tích hợp | cấp đăng ký có trách nhiệm tích hợp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_dang_ky_co_trach_nhiem_tich_hop</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3496,12 +3492,12 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>khong</t>
@@ -3524,39 +3520,39 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thu_hoi</t>
+          <t>map_khi_thay_cum_cap_dang_ky_co_trach_nhiem_tich_hop</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PRED_CAP_DANG_KY_CO_TRACH_NHIEM_TICH_HOP</t>
+          <t>PRED_VA_CAC_CO_QUAN_KHAC_GAY_PHIEN_HA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cấp đăng ký có trách nhiệm tích hợp</t>
+          <t>Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cấp đăng ký có trách nhiệm tích hợp | cấp đăng ký có trách nhiệm tích hợp với cơ quan đăng ký kinh doanh</t>
+          <t>Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà | Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>cap_dang_ky_co_trach_nhiem_tich_hop</t>
+          <t>va_cac_co_quan_khac_gay_phien_ha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3564,7 +3560,11 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>tổ chức</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>cơ quan đăng ký kinh doanh</t>
@@ -3592,24 +3592,24 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_dang_ky_co_trach_nhiem_tich_hop</t>
+          <t>map_khi_thay_cum_va_cac_co_quan_khac_gay_phien_ha;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRED_VIEC_BO_SUNG_THONG_TIN_VE_CHU_SO_HUU_HUONG_LOI_CUA_D</t>
+          <t>PRED_CAP_LAI_CHO_TO_CHUC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>việc bổ sung thông tin về chủ sở hữu hưởng lợi của doanh nghiệp (</t>
+          <t>cấp lại cho tổ chức</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>việc bổ sung thông tin về chủ sở hữu hưởng lợi của doanh nghiệp (</t>
+          <t>cấp lại cho tổ chức | cấp lại cho tổ chức với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>viec_bo_sung_thong_tin_ve_chu_so_huu_huong_loi_cua_doanh_nghiep</t>
+          <t>cap_lai_cho_to_chuc</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>chu_so_huu_huong_loi</t>
+          <t>hanh_dong_co_quan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3632,12 +3632,12 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>khong</t>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3660,39 +3660,39 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_viec_bo_sung_thong_tin_ve_chu_so_huu_huong_loi_cua_doanh_nghiep;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_thay_cum_cap_lai_cho_to_chuc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PRED_VA_CAC_CO_QUAN_KHAC_GAY_PHIEN_HA</t>
+          <t>PRED_KEM_THEO_TAI_LIEU_BANG_TIENG_NUOC_NGOAI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà</t>
+          <t>kèm theo tài liệu bằng tiếng nước ngoài.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà | Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà với cơ quan đăng ký kinh doanh</t>
+          <t>kèm theo tài liệu bằng tiếng nước ngoài.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>va_cac_co_quan_khac_gay_phien_ha</t>
+          <t>kem_theo_tai_lieu_bang_tieng_nuoc_ngoai</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3702,14 +3702,10 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>tổ chức</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>khong</t>
@@ -3717,7 +3713,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3732,39 +3728,39 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_va_cac_co_quan_khac_gay_phien_ha;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PRED_CAP_LAI_CHO_TO_CHUC</t>
+          <t>PRED_KEM_THEO_HO_SO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cấp lại cho tổ chức</t>
+          <t>kèm theo hồ sơ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>cấp lại cho tổ chức | cấp lại cho tổ chức với cơ quan đăng ký kinh doanh</t>
+          <t>kèm theo hồ sơ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>cap_lai_cho_to_chuc</t>
+          <t>kem_theo_ho_so</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3772,12 +3768,12 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>khong</t>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3800,24 +3796,24 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_lai_cho_to_chuc</t>
+          <t>map_khi_thay_cum_kem_theo_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_TAI_LIEU_BANG_TIENG_NUOC_NGOAI</t>
+          <t>PRED_VAN_BAN_UY_QUYEN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kèm theo tài liệu bằng tiếng nước ngoài.</t>
+          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kèm theo tài liệu bằng tiếng nước ngoài.</t>
+          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3827,7 +3823,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>kem_theo_tai_lieu_bang_tieng_nuoc_ngoai</t>
+          <t>van_ban_uy_quyen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3875,53 +3871,57 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_HO_SO</t>
+          <t>PRED_CAP_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kèm theo hồ sơ</t>
+          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kèm theo hồ sơ</t>
+          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng | cấp đăng ký doanh nghiệp theo quy trình dự phòng với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>kem_theo_ho_so</t>
+          <t>cap_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>dang_ky_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3931,65 +3931,61 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_kem_theo_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
+          <t>map_khi_thay_cum_cap_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PRED_VAN_BAN_UY_QUYEN</t>
+          <t>PRED_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
+          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
+          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp | đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>van_ban_uy_quyen</t>
+          <t>dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>ten_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4004,59 +4000,55 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PRED_CAP_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_NEU_CONG_TY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
+          <t>nếu công ty</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng | cấp đăng ký doanh nghiệp theo quy trình dự phòng với cơ quan đăng ký kinh doanh</t>
+          <t>nếu công ty</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>dieu_kien_ap_dung</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>cap_dang_ky_doanh_nghiep</t>
+          <t>neu_cong_ty</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>dieu_kien</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>công ty cổ phần</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>dang_ky_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>cổ đông sáng lập</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4071,29 +4063,29 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
+          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRED_TIEP_TUC_SU_DUNG_TEN_DOANH_NGHIEP_DA_DANG_KY_VA_KHON</t>
+          <t>PRED_LAP_DIA_DIEM_KINH_DOANH_DEN_CO_QUAN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>tiếp tục sử dụng tên doanh nghiệp đã đăng ký và không bắt buộc phải đăng ký đổi tên doanh nghiệp trong</t>
+          <t>lập địa điểm kinh doanh đến Cơ quan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>tiếp tục sử dụng tên doanh nghiệp đã đăng ký và không bắt buộc phải đăng ký đổi tên doanh nghiệp trong</t>
+          <t>lập địa điểm kinh doanh đến Cơ quan | lập địa điểm kinh doanh đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4103,12 +4095,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>tiep_tuc_su_dung_ten_doanh_nghiep_da_dang_ky_va_khong_bat_buoc_phai_dang_ky_doi_ten_doanh_nghiep_trong</t>
+          <t>lap_dia_diem_kinh_doanh_den_co_quan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ten_doanh_nghiep</t>
+          <t>chi_nhanh_van_phong_dai_dien</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4118,13 +4110,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>trường hợp có tên trùng</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>đăng ký kinh doanh cấp tỉnh nơi đặt địa điểm kinh doanh</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4139,51 +4135,59 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_tiep_tuc_su_dung_ten_doanh_nghiep_da_dang_ky_va_khong_bat_buoc_phai_dang_ky_doi_ten_doanh_nghiep_trong</t>
+          <t>map_khi_thay_cum_lap_dia_diem_kinh_doanh_den_co_quan;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_HOAT_DONG_CHI_NHANH</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp</t>
+          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp | đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh | cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>dang_ky_doanh_nghiep</t>
+          <t>cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ten_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+          <t>cap_giay</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>chi_nhanh</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4203,54 +4207,54 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PRED_NEU_CONG_TY</t>
+          <t>PRED_TIEP_NHAN_DE_NHAP_THONG_TIN_VAO_HE_THONG_THONG_TIN_Q</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nếu công ty</t>
+          <t>tiếp nhận để nhập thông tin vào Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>nếu công ty</t>
+          <t>tiếp nhận để nhập thông tin vào Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>tiep_nhan_ho_so</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>neu_cong_ty</t>
+          <t>tiep_nhan_de_nhap_thong_tin_vao_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>hanh_dong_co_quan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>công ty cổ phần</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>cổ đông sáng lập</t>
+          <t>Hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -4276,49 +4280,49 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_tiep_nhan_de_nhap_thong_tin_vao_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PRED_LAP_DIA_DIEM_KINH_DOANH_DEN_CO_QUAN</t>
+          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA_CHO_NGU</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>lập địa điểm kinh doanh đến Cơ quan</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>lập địa điểm kinh doanh đến Cơ quan | lập địa điểm kinh doanh đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>lap_dia_diem_kinh_doanh_den_co_quan</t>
+          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>đăng ký kinh doanh cấp tỉnh nơi đặt địa điểm kinh doanh</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4328,7 +4332,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4343,54 +4347,54 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_lap_dia_diem_kinh_doanh_den_co_quan;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_HOAT_DONG_CHI_NHANH</t>
+          <t>PRED_DUNG_THUC_HIEN_THU_TUC_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
+          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh | cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp | dừng thực hiện thủ tục đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
+          <t>dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>người thành lập doanh nghiệp</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>chi_nhanh</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4415,60 +4419,64 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PRED_TIEP_NHAN_DE_NHAP_THONG_TIN_VAO_HE_THONG_THONG_TIN_Q</t>
+          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>tiếp nhận để nhập thông tin vào Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>tiếp nhận để nhập thông tin vào Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiep_nhan_ho_so</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>tiep_nhan_de_nhap_thong_tin_vao_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hồ sơ đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4488,24 +4496,24 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_tiep_nhan_de_nhap_thong_tin_vao_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA_CHO_NGU</t>
+          <t>PRED_HO_SO_BAO_GOM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ.</t>
+          <t>hồ sơ bao gồm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>hồ sơ bao gồm | hồ sơ bao gồm với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4515,7 +4523,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>ho_so_bao_gom</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4525,12 +4533,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>công ty</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
+          <t>nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4545,7 +4553,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4560,49 +4568,49 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>map_khi_thay_cum_ho_so_bao_gom;thuong_di_kem_thanh_phan_ho_so</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PRED_DUNG_THUC_HIEN_THU_TUC_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_CAC_GIAY_TO_SAU_DAY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp</t>
+          <t>các giấy tờ sau đây</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp | dừng thực hiện thủ tục đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>các giấy tờ sau đây | các giấy tờ sau đây với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep</t>
+          <t>cac_giay_to_sau_day</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
+          <t>công ty</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
+          <t>nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4612,12 +4620,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4632,24 +4640,24 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA</t>
+          <t>PRED_GUI_GIAY_DE_NGHI_DANG_KY_THAY_DOI_VON_DAU_TU_DEN_CO_</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả</t>
+          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan | gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4659,7 +4667,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua</t>
+          <t>gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4669,12 +4677,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>giấy đề nghị</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4684,7 +4692,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4704,44 +4712,44 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PRED_HO_SO_BAO_GOM</t>
+          <t>PRED_TRA_LE_PHI_DANG_KY_DOANH_NGHIEP_VA_PHI_CONG_BO_NOI_D</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hồ sơ bao gồm</t>
+          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>hồ sơ bao gồm | hồ sơ bao gồm với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cong_bo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ho_so_bao_gom</t>
+          <t>tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cong_bo</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4749,11 +4757,7 @@
           <t>nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>khong</t>
@@ -4761,7 +4765,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4776,24 +4780,24 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_ho_so_bao_gom;thuong_di_kem_thanh_phan_ho_so</t>
+          <t>map_khi_thay_cum_tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PRED_CAC_GIAY_TO_SAU_DAY</t>
+          <t>PRED_KEM_THEO_VAN_BAN_GIAI_TRINH_CUA_DOANH_NGHIEP_VE_LY_D</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>các giấy tờ sau đây</t>
+          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>các giấy tờ sau đây | các giấy tờ sau đây với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận | kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4803,7 +4807,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>cac_giay_to_sau_day</t>
+          <t>kem_theo_van_ban_giai_trinh_cua_doanh_nghiep_ve_ly_do_dang_ky_thay_doi_va_duoc_co_quan_dang_ky_kinh_doanh_cap_tinh_chap_thuan</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4813,7 +4817,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4855,42 +4859,38 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PRED_GUI_GIAY_DE_NGHI_DANG_KY_THAY_DOI_VON_DAU_TU_DEN_CO_</t>
+          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CHI_NHANH</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan | gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan | thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
+          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
+          <t>chi_nhanh_van_phong_dai_dien</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>giấy đề nghị</t>
+          <t>thực hiện</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4920,52 +4920,52 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
+          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRED_TRA_LE_PHI_DANG_KY_DOANH_NGHIEP_VA_PHI_CONG_BO_NOI_D</t>
+          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CUA_TAT_CA_DIA_</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan | thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>cong_bo</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
+          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>cong_bo</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
+          <t>chi_nhanh_van_phong_dai_dien</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>thực hiện</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>khong</t>
@@ -4988,49 +4988,49 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
+          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_VAN_BAN_GIAI_TRINH_CUA_DOANH_NGHIEP_VE_LY_D</t>
+          <t>PRED_THONG_BAO_CHO_CO_QUAN_QUAN_LY_THUE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận</t>
+          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận | kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế | cấp tỉnh thông báo cho Cơ quan quản lý thuế với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>kem_theo_van_ban_giai_trinh_cua_doanh_nghiep_ve_ly_do_dang_ky_thay_doi_va_duoc_co_quan_dang_ky_kinh_doanh_cap_tinh_chap_thuan</t>
+          <t>thong_bao_cho_co_quan_quan_ly_thue</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5060,45 +5060,49 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_thong_bao_cho_co_quan_quan_ly_thue;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CHI_NHANH</t>
+          <t>PRED_HUY_BO_QUYET_DINH_THU_HOI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan</t>
+          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan | thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp | cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
+          <t>huy_bo_quyet_dinh_thu_hoi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>thu_hoi</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>thực hiện</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5108,7 +5112,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5128,50 +5132,54 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
+          <t>map_khi_thay_cum_huy_bo_quyet_dinh_thu_hoi;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CUA_TAT_CA_DIA_</t>
+          <t>PRED_CO_QUAN_DANG_KY_KINH_DOANH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan</t>
+          <t>Cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan | thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>Cơ quan đăng ký kinh doanh | Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
+          <t>co_quan_dang_ky_kinh_doanh</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>dang_ky</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>thực hiện</t>
+          <t>cấp xã và các cơ quan khác gây phiền hà đối với tổ chức</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5196,59 +5204,59 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
+          <t>map_khi_thay_cum_co_quan_dang_ky_kinh_doanh;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_XA_TIEP_NHAN_HO_SO_DANG_KY_HO_KINH_DOANH_VAO_HE_THON</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>đăng ký kinh doanh cấp tỉnh ra thông báo về việc vi phạm của doanh nghiệp và quyết định thu hồi Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>đăng ký kinh doanh cấp tỉnh ra thông báo về việc vi phạm của doanh nghiệp và quyết định thu hồi Giấy chứng nhận đăng ký doanh nghiệp | đăng ký kinh doanh cấp tỉnh ra thông báo về việc vi phạm của doanh nghiệp và quyết định thu hồi Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh | xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>dang_ky_doanh_nghiep</t>
+          <t>xa_tiep_nhan_ho_so_dang_ky_ho_kinh_doanh_vao_he_thong_thong_tin_ve_dang_ky_ho_kinh_doanh</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>thời hạn 03 ngày làm việc kể từ ngày nhận được giấy tờ quy định tại khoản 2 Điều 68 Nghị định này</t>
+          <t>hồ sơ đáp ứng các điều kiện sau đây:</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5263,368 +5271,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky_doanh_nghiep;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>PRED_THONG_BAO_CHO_CO_QUAN_QUAN_LY_THUE</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế | cấp tỉnh thông báo cho Cơ quan quản lý thuế với cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>thong_bao</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>thong_bao_cho_co_quan_quan_ly_thue</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>thong_bao</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_thong_bao_cho_co_quan_quan_ly_thue;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>PRED_HUY_BO_QUYET_DINH_THU_HOI</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp | cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>huy_bo_quyet_dinh_thu_hoi</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_huy_bo_quyet_dinh_thu_hoi;thuong_di_kem_thoi_han</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>PRED_CO_QUAN_DANG_KY_KINH_DOANH</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Cơ quan đăng ký kinh doanh | Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>dang_ky</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>co_quan_dang_ky_kinh_doanh</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>dang_ky</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>cấp xã và các cơ quan khác gây phiền hà đối với tổ chức</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_co_quan_dang_ky_kinh_doanh;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>PRED_XA_TIEP_NHAN_HO_SO_DANG_KY_HO_KINH_DOANH_VAO_HE_THON</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh | xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh với cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>xa_tiep_nhan_ho_so_dang_ky_ho_kinh_doanh_vao_he_thong_thong_tin_ve_dang_ky_ho_kinh_doanh</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>hồ sơ đáp ứng các điều kiện sau đây:</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
           <t>map_khi_thay_cum_xa_tiep_nhan_ho_so_dang_ky_ho_kinh_doanh_vao_he_thong_thong_tin_ve_dang_ky_ho_kinh_doanh</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>PRED_CAP_CO_SU_DUNG_THONG_TIN_TU_CHUNG_MINH_NHAN_DAN</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>cấp có sử dụng thông tin từ chứng minh nhân dân</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>cấp có sử dụng thông tin từ chứng minh nhân dân | cấp có sử dụng thông tin từ chứng minh nhân dân với cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>khac</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>cap_co_su_dung_thong_tin_tu_chung_minh_nhan_dan</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>hanh_dong_co_quan</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_cap_co_su_dung_thong_tin_tu_chung_minh_nhan_dan</t>
         </is>
       </c>
     </row>

--- a/data/processed/ontology/enterprise/predicate_lexicon.xlsx
+++ b/data/processed/ontology/enterprise/predicate_lexicon.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRED_UY_QUYEN_BANG_VAN_BAN</t>
+          <t>PRED_THONG_BAO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ủy quyền.</t>
+          <t>thông báo cho công ty và chỉ có hiệu lực đối với công ty</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ủy quyền.</t>
+          <t>thông báo cho công ty và chỉ có hiệu lực đối với công ty | thông báo cho công ty và chỉ có hiệu lực đối với công ty với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yeu_cau_bao_cao</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>uy_quyen_bang_van_ban</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>uy_quyen_va_lay_y_kien</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>phần vốn góp</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>kể từ ngày công ty nhận được văn bản</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>khong</t>
@@ -627,54 +631,54 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_uy_quyen_bang_van_ban</t>
+          <t>map_khi_thay_cum_thong_bao;khong_dong_nhat_voi_cong_bo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRED_THONG_BAO</t>
+          <t>PRED_XEM_XET_TINH_HOP_LE_CUA_HO_SO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>thông báo cho công ty và chỉ có hiệu lực đối với công ty</t>
+          <t>xem xét tính hợp lệ của hồ sơ đăng ký doanh nghiệp và cấp đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>thông báo cho công ty và chỉ có hiệu lực đối với công ty | thông báo cho công ty và chỉ có hiệu lực đối với công ty với cơ quan đăng ký kinh doanh</t>
+          <t>xem xét tính hợp lệ của hồ sơ đăng ký doanh nghiệp và cấp đăng ký doanh nghiệp | xem xét tính hợp lệ của hồ sơ đăng ký doanh nghiệp và cấp đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>xem_xet_tinh_hop_le_cua_ho_so</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>kể từ ngày công ty nhận được văn bản</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -684,7 +688,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -704,59 +708,59 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thong_bao;khong_dong_nhat_voi_cong_bo</t>
+          <t>map_khi_thay_cum_xem_xet_tinh_hop_le_cua_ho_so;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRED_XEM_XET_TINH_HOP_LE_CUA_HO_SO</t>
+          <t>PRED_DANG_KY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>xem xét tính hợp lệ của hồ sơ đăng ký doanh nghiệp và cấp đăng ký doanh nghiệp</t>
+          <t>đăng ký với Cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>xem xét tính hợp lệ của hồ sơ đăng ký doanh nghiệp và cấp đăng ký doanh nghiệp | xem xét tính hợp lệ của hồ sơ đăng ký doanh nghiệp và cấp đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>đăng ký với Cơ quan đăng ký kinh doanh | đăng ký với Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>xem_xet_tinh_hop_le_cua_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -771,29 +775,29 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_xem_xet_tinh_hop_le_cua_ho_so;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_dang_ky;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY</t>
+          <t>PRED_DANG_KY_THAY_DOI_NOI_DUNG_GIAY_CHUNG_NHAN_DANG_KY_DO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>đăng ký với Cơ quan đăng ký kinh doanh</t>
+          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>đăng ký với Cơ quan đăng ký kinh doanh | đăng ký với Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
+          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -803,14 +807,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>dang_ky</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>dang_ky</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
@@ -821,14 +825,10 @@
           <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -843,49 +843,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
+          <t>map_khi_thay_cum_dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY_THAY_DOI_NOI_DUNG_GIAY_CHUNG_NHAN_DANG_KY_DO</t>
+          <t>PRED_XEM_XET_VA_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP_</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp mới theo nội dung bản án</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp mới theo nội dung bản án | xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp mới theo nội dung bản án với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>tham_dinh_ho_so</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi_theo_noi_dung_ban_an</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>hanh_dong_co_quan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -893,7 +893,11 @@
           <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>co</t>
@@ -916,56 +920,56 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi_theo_noi_dung_ban_an;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRED_XEM_XET_VA_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP_</t>
+          <t>PRED_THONG_BAO_THAY_DOI_NOI_DUNG_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp mới theo nội dung bản án</t>
+          <t>thông báo thay đổi nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp mới theo nội dung bản án | xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp mới theo nội dung bản án với cơ quan đăng ký kinh doanh</t>
+          <t>thông báo thay đổi nội dung đăng ký doanh nghiệp | thông báo thay đổi nội dung đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>tham_dinh_ho_so</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi_theo_noi_dung_ban_an</t>
+          <t>thong_bao_thay_doi_noi_dung_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nội dung đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>co</t>
@@ -988,64 +992,56 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi_theo_noi_dung_ban_an;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_thong_bao_thay_doi_noi_dung_dang_ky_doanh_nghiep;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRED_THONG_BAO_THAY_DOI_NOI_DUNG_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_THANH_PHAN_HO_SO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>thông báo thay đổi nội dung đăng ký doanh nghiệp</t>
+          <t>thành phần hồ sơ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>thông báo thay đổi nội dung đăng ký doanh nghiệp | thông báo thay đổi nội dung đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>thành phần hồ sơ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>thong_bao_thay_doi_noi_dung_dang_ky_doanh_nghiep</t>
+          <t>thanh_phan_ho_so</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>thong_bao</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
+          <t>nop_ho_so</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>ho_so</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,24 +1056,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thong_bao_thay_doi_noi_dung_dang_ky_doanh_nghiep;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_thanh_phan_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PRED_THANH_PHAN_HO_SO</t>
+          <t>PRED_KEM_THEO_CUM_TU_CHI_NHANH_DOI_VOI_CHI_NHANH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>thành phần hồ sơ</t>
+          <t>kèm theo cụm từ “Chi nhánh” đối với chi nhánh, cụm từ “Văn phòng đại diện”</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>thành phần hồ sơ | thành phần hồ sơ với cơ quan đăng ký kinh doanh</t>
+          <t>kèm theo cụm từ “Chi nhánh” đối với chi nhánh, cụm từ “Văn phòng đại diện”</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1087,7 +1083,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>thanh_phan_ho_so</t>
+          <t>kem_theo_cum_tu_chi_nhanh_doi_voi_chi_nhanh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1095,24 +1091,16 @@
           <t>nop_ho_so</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>công ty cổ phần</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ho_so</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>chi_nhanh</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1127,57 +1115,57 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thanh_phan_ho_so;thuong_di_kem_thoi_han;thuong_di_kem_thanh_phan_ho_so</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRED_THONG_BAO</t>
+          <t>PRED_DANG_KY_THAY_DOI_NOI_DUNG_GIAY_CHUNG_NHAN_DANG_KY_HO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thông báo phải bao gồm các nội dung sau đây</t>
+          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thông báo phải bao gồm các nội dung sau đây | Thông báo phải bao gồm các nội dung sau đây với cơ quan đăng ký kinh doanh</t>
+          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>chi_nhanh_van_phong_dai_dien</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>công ty cổ phần</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>chi_nhanh</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>co</t>
@@ -1185,7 +1173,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1200,39 +1188,39 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_DIA_DIEM_KINH_DOANH_DEN_CO_QUAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp phải thông báo công khai trên Cổng thông tin quốc gia về đăng ký doanh nghiệp và phải nộp phí</t>
+          <t>địa điểm kinh doanh đến Cơ quan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp phải thông báo công khai trên Cổng thông tin quốc gia về đăng ký doanh nghiệp và phải nộp phí | cấp Giấy chứng nhận đăng ký doanh nghiệp phải thông báo công khai trên Cổng thông tin quốc gia về đăng ký doanh nghiệp và phải nộp phí với cơ quan đăng ký kinh doanh</t>
+          <t>địa điểm kinh doanh đến Cơ quan | địa điểm kinh doanh đến Cơ quan với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>dia_diem_kinh_doanh_den_co_quan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>chi_nhanh_van_phong_dai_dien</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1242,7 +1230,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1252,7 +1240,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1267,29 +1255,29 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>map_khi_thay_cum_dia_diem_kinh_doanh_den_co_quan;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PRED_NGUOI_GOP_VON_PHAI_LAM_THU_TUC_CHUYEN_QUYEN_SO_HUU_T</t>
+          <t>PRED_GOP_VON_CHO_CONG_TY_DU_VA_DUNG_LOAI_TAI_SAN_DA_CAM_K</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>người góp vốn phải làm thủ tục chuyển quyền sở hữu tài sản đó hoặc quyền sử dụng đất cho công ty</t>
+          <t>góp vốn cho công ty đủ và đúng loại tài sản đã cam kết</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>người góp vốn phải làm thủ tục chuyển quyền sở hữu tài sản đó hoặc quyền sử dụng đất cho công ty</t>
+          <t>góp vốn cho công ty đủ và đúng loại tài sản đã cam kết</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1299,7 +1287,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>nguoi_gop_von_phai_lam_thu_tuc_chuyen_quyen_so_huu_tai_san_do_hoac_quyen_su_dung_dat_cho_cong_ty</t>
+          <t>gop_von_cho_cong_ty_du_va_dung_loai_tai_san_da_cam_ket</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1314,13 +1302,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>thủ tục</t>
+          <t>đăng ký thành lập doanh nghiệp trong thời hạn 90 ngày kể từ ngày được cấp Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1335,54 +1323,54 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_nguoi_gop_von_phai_lam_thu_tuc_chuyen_quyen_so_huu_tai_san_do_hoac_quyen_su_dung_dat_cho_cong_ty</t>
+          <t>map_khi_thay_cum_gop_von_cho_cong_ty_du_va_dung_loai_tai_san_da_cam_ket;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PRED_GIA_TRI_TAI_SAN_GOP_VON_PHAI_DUOC_TREN_50_SO_THANH_V</t>
+          <t>PRED_CAP_NHAT_THAY_DOI_THANH_VIEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>giá trị tài sản góp vốn phải được trên 50% số thành viên</t>
+          <t>cập nhật kịp thời thay đổi thành viên trong sổ đăng ký thành viên theo yêu cầu của thành viên có liên quan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>giá trị tài sản góp vốn phải được trên 50% số thành viên</t>
+          <t>cập nhật kịp thời thay đổi thành viên trong sổ đăng ký thành viên theo yêu cầu của thành viên có liên quan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_nhat</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>gia_tri_tai_san_gop_von_phai_duoc_tren_50_so_thanh_vien</t>
+          <t>cap_nhat_thay_doi_thanh_vien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>von_va_gop_von</t>
+          <t>cap_nhat</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>công ty</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>cổ đông sáng lập</t>
+          <t>quy định tại Điều lệ công ty</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1403,29 +1391,29 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gia_tri_tai_san_gop_von_phai_duoc_tren_50_so_thanh_vien</t>
+          <t>map_khi_thay_cum_cap_nhat_thay_doi_thanh_vien</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_CUM_TU_CHI_NHANH_DOI_VOI_CHI_NHANH</t>
+          <t>PRED_GUI_PHIEU_LAY_Y_KIEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>kèm theo cụm từ “Chi nhánh” đối với chi nhánh, cụm từ “Văn phòng đại diện”</t>
+          <t>gửi phiếu lấy ý kiến về công ty</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kèm theo cụm từ “Chi nhánh” đối với chi nhánh, cụm từ “Văn phòng đại diện”</t>
+          <t>gửi phiếu lấy ý kiến về công ty</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1435,18 +1423,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>kem_theo_cum_tu_chi_nhanh_doi_voi_chi_nhanh</t>
+          <t>gui_phieu_lay_y_kien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>uy_quyen_va_lay_y_kien</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>công ty</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>chi_nhanh</t>
+          <t>gửi phiếu</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1457,7 +1449,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1467,29 +1459,29 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_gui_phieu_lay_y_kien</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY_THAY_DOI_NOI_DUNG_GIAY_CHUNG_NHAN_DANG_KY_HO</t>
+          <t>PRED_DANG_KY_THAY_DOI_NOI_DUNG_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
+          <t>đăng ký thay đổi nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi nội dung Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
+          <t>đăng ký thay đổi nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1499,22 +1491,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
+          <t>dang_ky_thay_doi_noi_dung_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>công ty</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>chi_nhanh</t>
+          <t>nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1540,49 +1532,49 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky_thay_doi_noi_dung_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_dang_ky_thay_doi_noi_dung_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PRED_DIA_DIEM_KINH_DOANH_DEN_CO_QUAN</t>
+          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>địa điểm kinh doanh đến Cơ quan</t>
+          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>địa điểm kinh doanh đến Cơ quan | địa điểm kinh doanh đến Cơ quan với cơ quan đăng ký kinh doanh</t>
+          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp. | cấp Giấy chứng nhận đăng ký doanh nghiệp. với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>dia_diem_kinh_doanh_den_co_quan</t>
+          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>công ty cổ phần</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>đăng ký kinh doanh</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1592,7 +1584,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1612,55 +1604,55 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dia_diem_kinh_doanh_den_co_quan;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRED_GOP_VON_CHO_CONG_TY_DU_VA_DUNG_LOAI_TAI_SAN_DA_CAM_K</t>
+          <t>PRED_CUNG_NHAU_DANG_KY_MUA_IT_NHAT_20_TONG_SO_CO_PHAN_PHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>góp vốn cho công ty đủ và đúng loại tài sản đã cam kết</t>
+          <t>cùng nhau đăng ký mua ít nhất 20% tổng số cổ phần phổ thông được quyền chào bán</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>góp vốn cho công ty đủ và đúng loại tài sản đã cam kết</t>
+          <t>cùng nhau đăng ký mua ít nhất 20% tổng số cổ phần phổ thông được quyền chào bán</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>gop_von_cho_cong_ty_du_va_dung_loai_tai_san_da_cam_ket</t>
+          <t>cung_nhau_dang_ky_mua_it_nhat_20_tong_so_co_phan_pho_thong_duoc_quyen_chao_ban</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>von_va_gop_von</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>đăng ký thành lập doanh nghiệp trong thời hạn 90 ngày kể từ ngày được cấp Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>đăng ký thành lập doanh nghiệp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1680,24 +1672,24 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gop_von_cho_cong_ty_du_va_dung_loai_tai_san_da_cam_ket;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_cung_nhau_dang_ky_mua_it_nhat_20_tong_so_co_phan_pho_thong_duoc_quyen_chao_ban;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PRED_CAP_NHAT_THAY_DOI_THANH_VIEN</t>
+          <t>PRED_CAP_NHAT_THONG_TIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cập nhật kịp thời thay đổi thành viên trong sổ đăng ký thành viên theo yêu cầu của thành viên có liên quan</t>
+          <t>cập nhật kịp thời thay đổi cổ đông trong sổ đăng ký cổ đông theo yêu cầu của cổ đông có liên quan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cập nhật kịp thời thay đổi thành viên trong sổ đăng ký thành viên theo yêu cầu của thành viên có liên quan</t>
+          <t>cập nhật kịp thời thay đổi cổ đông trong sổ đăng ký cổ đông theo yêu cầu của cổ đông có liên quan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1707,7 +1699,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>cap_nhat_thay_doi_thanh_vien</t>
+          <t>cap_nhat_thong_tin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1722,7 +1714,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>quy định tại Điều lệ công ty</t>
+          <t>cầu của</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1748,44 +1740,44 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_nhat_thay_doi_thanh_vien</t>
+          <t>map_khi_thay_cum_cap_nhat_thong_tin</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PRED_RUT_VON_DA_GOP_RA_KHOI_CONG_TY_DUOI_MOI_HINH_THUC</t>
+          <t>PRED_KEM_THEO_CHUNG_QUYEN_RIENG_LE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rút vốn đã góp ra khỏi công ty dưới mọi hình thức</t>
+          <t>kèm theo chứng quyền riêng lẻ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rút vốn đã góp ra khỏi công ty dưới mọi hình thức</t>
+          <t>kèm theo chứng quyền riêng lẻ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>rut_von_da_gop_ra_khoi_cong_ty_duoi_moi_hinh_thuc</t>
+          <t>kem_theo_chung_quyen_rieng_le</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>von_va_gop_von</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1797,12 +1789,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1812,39 +1804,39 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_rut_von_da_gop_ra_khoi_cong_ty_duoi_moi_hinh_thuc;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRED_GUI_PHIEU_LAY_Y_KIEN</t>
+          <t>PRED_NEU_DIEU_LE_CONG_TY_KHONG_QUY_DINH_THOI_HAN_DAI_HON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gửi phiếu lấy ý kiến về công ty</t>
+          <t>nếu Điều lệ công ty không quy định thời hạn dài hơn.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gửi phiếu lấy ý kiến về công ty</t>
+          <t>nếu Điều lệ công ty không quy định thời hạn dài hơn. | nếu Điều lệ công ty không quy định thời hạn dài hơn. với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dieu_kien_ap_dung</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>gui_phieu_lay_y_kien</t>
+          <t>neu_dieu_le_cong_ty_khong_quy_dinh_thoi_han_dai_hon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>uy_quyen_va_lay_y_kien</t>
+          <t>dieu_kien</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1854,13 +1846,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>gửi phiếu</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>danh sách cổ đông</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1880,39 +1876,39 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_phieu_lay_y_kien</t>
+          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY_THAY_DOI_NOI_DUNG_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_NEU_DIEU_LE_CONG_TY_KHONG_QUY_DINH_KHAC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi nội dung đăng ký doanh nghiệp</t>
+          <t>nếu Điều lệ công ty không quy định khác</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi nội dung đăng ký doanh nghiệp</t>
+          <t>nếu Điều lệ công ty không quy định khác | nếu Điều lệ công ty không quy định khác với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>dieu_kien_ap_dung</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>dang_ky_thay_doi_noi_dung_dang_ky_doanh_nghiep</t>
+          <t>neu_dieu_le_cong_ty_khong_quy_dinh_khac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>dieu_kien</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1922,10 +1918,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>từ ngày</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>co</t>
@@ -1943,44 +1943,44 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky_thay_doi_noi_dung_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
+          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRED_CONG_BO_TREN_TRANG_THONG_TIN_DIEN_TU</t>
+          <t>PRED_GUI_VE_CONG_TY_PHIEU_LAY_Y_KIEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>công bố trên trang thông tin điện tử, ấn phẩm (</t>
+          <t>gửi về công ty phiếu lấy ý kiến</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>công bố trên trang thông tin điện tử, ấn phẩm (</t>
+          <t>gửi về công ty phiếu lấy ý kiến</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>cong_bo</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>cong_bo_tren_trang_thong_tin_dien_tu</t>
+          <t>gui_ve_cong_ty_phieu_lay_y_kien</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>cong_bo</t>
+          <t>uy_quyen_va_lay_y_kien</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1988,7 +1988,11 @@
           <t>công ty</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>gửi về</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -2012,39 +2016,39 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cong_bo_tren_trang_thong_tin_dien_tu</t>
+          <t>map_khi_thay_cum_gui_ve_cong_ty_phieu_lay_y_kien</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRED_NEU_CO_VA_NIEM_YET_CONG_KHAI_TAI_TRU_SO_CHINH</t>
+          <t>PRED_TIEP_NHAN_THEM_THANH_VIEN_HOP_DANH_HOAC_THANH_VIEN_G</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nếu có) và niêm yết công khai tại trụ sở chính, địa điểm kinh doanh của công ty về các thông tin bất thường</t>
+          <t>tiếp nhận thêm thành viên hợp danh hoặc thành viên góp vốn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nếu có) và niêm yết công khai tại trụ sở chính, địa điểm kinh doanh của công ty về các thông tin bất thường</t>
+          <t>tiếp nhận thêm thành viên hợp danh hoặc thành viên góp vốn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>tiep_nhan_ho_so</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>neu_co_va_niem_yet_cong_khai_tai_tru_so_chinh</t>
+          <t>tiep_nhan_them_thanh_vien_hop_danh_hoac_thanh_vien_gop_von</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>hanh_dong_co_quan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2076,55 +2080,55 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_tiep_nhan_them_thanh_vien_hop_danh_hoac_thanh_vien_gop_von</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRED_CUNG_NHAU_DANG_KY_MUA_IT_NHAT_20_TONG_SO_CO_PHAN_PHO</t>
+          <t>PRED_NOP_DU_SO_VON_CAM_KET_GOP_VAO_CONG_TY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cùng nhau đăng ký mua ít nhất 20% tổng số cổ phần phổ thông được quyền chào bán</t>
+          <t>nộp đủ số vốn cam kết góp vào công ty</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cùng nhau đăng ký mua ít nhất 20% tổng số cổ phần phổ thông được quyền chào bán</t>
+          <t>nộp đủ số vốn cam kết góp vào công ty</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>cung_nhau_dang_ky_mua_it_nhat_20_tong_so_co_phan_pho_thong_duoc_quyen_chao_ban</t>
+          <t>nop_du_so_von_cam_ket_gop_vao_cong_ty</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>von_va_gop_von</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>công ty</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>đăng ký thành lập doanh nghiệp</t>
+          <t>thời hạn 15 ngày kể từ ngày được chấp thuận</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2134,65 +2138,69 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cung_nhau_dang_ky_mua_it_nhat_20_tong_so_co_phan_pho_thong_duoc_quyen_chao_ban;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
+          <t>map_khi_thay_cum_nop_du_so_von_cam_ket_gop_vao_cong_ty;thuong_di_kem_thoi_han;co_ngoai_le_can_xu_ly_rieng</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRED_CAP_NHAT_THONG_TIN</t>
+          <t>PRED_XEM_XET_VA_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cập nhật kịp thời thay đổi cổ đông trong sổ đăng ký cổ đông theo yêu cầu của cổ đông có liên quan</t>
+          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cập nhật kịp thời thay đổi cổ đông trong sổ đăng ký cổ đông theo yêu cầu của cổ đông có liên quan</t>
+          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp | xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cap_nhat</t>
+          <t>tham_dinh_ho_so</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>cap_nhat_thong_tin</t>
+          <t>xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>cap_nhat</t>
+          <t>hanh_dong_co_quan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>cầu của</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2207,61 +2215,69 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_nhat_thong_tin</t>
+          <t>map_khi_thay_cum_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_CHUNG_QUYEN_RIENG_LE</t>
+          <t>PRED_NEU_CO_DU_DIEU_KIEN_QUY_DINH_TAI_KHOAN_1_DIEU_NAY_VA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kèm theo chứng quyền riêng lẻ</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kèm theo chứng quyền riêng lẻ</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dieu_kien_ap_dung</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>kem_theo_chung_quyen_rieng_le</t>
+          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dieu_kien</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2271,29 +2287,29 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PRED_NEU_DIEU_LE_CONG_TY_KHONG_QUY_DINH_THOI_HAN_DAI_HON</t>
+          <t>PRED_NEU_CO_DU_DIEU_KIEN_QUY_DINH_TAI_KHOAN_1_DIEU_NAY_VA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nếu Điều lệ công ty không quy định thời hạn dài hơn.</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nếu Điều lệ công ty không quy định thời hạn dài hơn. | nếu Điều lệ công ty không quy định thời hạn dài hơn. với cơ quan đăng ký kinh doanh</t>
+          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2303,7 +2319,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>neu_dieu_le_cong_ty_khong_quy_dinh_thoi_han_dai_hon</t>
+          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2313,12 +2329,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>danh sách cổ đông</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2343,7 +2359,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2355,42 +2371,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PRED_NEU_DIEU_LE_CONG_TY_KHONG_QUY_DINH_KHAC</t>
+          <t>PRED_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nếu Điều lệ công ty không quy định khác</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nếu Điều lệ công ty không quy định khác | nếu Điều lệ công ty không quy định khác với cơ quan đăng ký kinh doanh</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp | Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>neu_dieu_le_cong_ty_khong_quy_dinh_khac</t>
+          <t>giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>từ ngày</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2415,29 +2431,29 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_giay_chung_nhan_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PRED_GUI_VE_CONG_TY_PHIEU_LAY_Y_KIEN</t>
+          <t>PRED_GUI_HO_SO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gửi về công ty phiếu lấy ý kiến</t>
+          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>gửi về công ty phiếu lấy ý kiến</t>
+          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh | gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2447,28 +2463,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>gui_ve_cong_ty_phieu_lay_y_kien</t>
+          <t>gui_ho_so</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>uy_quyen_va_lay_y_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>gửi về</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>thời hạn</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2488,49 +2508,49 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_ve_cong_ty_phieu_lay_y_kien</t>
+          <t>map_khi_thay_cum_gui_ho_so;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PRED_CHUYEN_MOT_PHAN_HOAC_TOAN_BO_PHAN_VON_GOP_CUA_MINH_T</t>
+          <t>PRED_THU_HOI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>chuyển một phần hoặc toàn bộ phần vốn góp của mình tại công ty cho tổ chức, cá nhân khác</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>chuyển một phần hoặc toàn bộ phần vốn góp của mình tại công ty cho tổ chức, cá nhân khác</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>chuyen_mot_phan_hoac_toan_bo_phan_von_gop_cua_minh_tai_cong_ty_cho_to_chuc</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>von_va_gop_von</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>phần vốn góp</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -2546,7 +2566,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2556,49 +2576,49 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_chuyen_mot_phan_hoac_toan_bo_phan_von_gop_cua_minh_tai_cong_ty_cho_to_chuc;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_thay_cum_thu_hoi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PRED_NEU_KHONG_DUOC_SU_CHAP_THUAN_CUA_CAC_THANH_VIEN_HOP_</t>
+          <t>PRED_KEM_THEO_HO_SO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nếu không được sự chấp thuận của các thành viên hợp danh còn lại.</t>
+          <t>kèm theo hồ sơ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>nếu không được sự chấp thuận của các thành viên hợp danh còn lại.</t>
+          <t>kèm theo hồ sơ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>neu_khong_duoc_su_chap_thuan_cua_cac_thanh_vien_hop_danh_con_lai</t>
+          <t>kem_theo_ho_so</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>phần vốn góp</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -2609,12 +2629,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2624,49 +2644,49 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_kem_theo_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PRED_NEU_TAI_SAN_CUA_CONG_TY_KHONG_DU_DE_TRANG_TRAI_SO_NO</t>
+          <t>PRED_VAN_BAN_UY_QUYEN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nếu tài sản của công ty không đủ để trang trải số nợ của công ty</t>
+          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nếu tài sản của công ty không đủ để trang trải số nợ của công ty</t>
+          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>neu_tai_san_cua_cong_ty_khong_du_de_trang_trai_so_no_cua_cong_ty</t>
+          <t>van_ban_uy_quyen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>tài sản của công ty không đủ để trang trải số nợ của công ty</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2677,7 +2697,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2692,48 +2712,56 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PRED_TIEP_NHAN_THEM_THANH_VIEN_HOP_DANH_HOAC_THANH_VIEN_G</t>
+          <t>PRED_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>tiếp nhận thêm thành viên hợp danh hoặc thành viên góp vốn</t>
+          <t>đăng ký doanh nghiệp thì việc ủy quyền thực hiện</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>tiếp nhận thêm thành viên hợp danh hoặc thành viên góp vốn</t>
+          <t>đăng ký doanh nghiệp thì việc ủy quyền thực hiện | đăng ký doanh nghiệp thì việc ủy quyền thực hiện với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiep_nhan_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>tiep_nhan_them_thanh_vien_hop_danh_hoac_thanh_vien_gop_von</t>
+          <t>dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>uy_quyen_va_lay_y_kien</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>công ty</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>tục đăng</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>khong</t>
@@ -2756,55 +2784,59 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_tiep_nhan_them_thanh_vien_hop_danh_hoac_thanh_vien_gop_von</t>
+          <t>map_khi_thay_cum_dang_ky_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PRED_NOP_DU_SO_VON_CAM_KET_GOP_VAO_CONG_TY</t>
+          <t>PRED_UY_QUYEN_BANG_VAN_BAN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nộp đủ số vốn cam kết góp vào công ty</t>
+          <t>ủy quyền thực hiện</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nộp đủ số vốn cam kết góp vào công ty</t>
+          <t>ủy quyền thực hiện | ủy quyền thực hiện với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>yeu_cau_bao_cao</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>nop_du_so_von_cam_ket_gop_vao_cong_ty</t>
+          <t>uy_quyen_bang_van_ban</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>von_va_gop_von</t>
+          <t>uy_quyen_va_lay_y_kien</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>thời hạn 15 ngày kể từ ngày được chấp thuận</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>quy định tại khoản 2 Điều này</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2814,7 +2846,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2824,51 +2856,59 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_nop_du_so_von_cam_ket_gop_vao_cong_ty;thuong_di_kem_thoi_han;co_ngoai_le_can_xu_ly_rieng</t>
+          <t>map_khi_thay_cum_uy_quyen_bang_van_ban</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PRED_CUNG_NHAU_GOP_VON</t>
+          <t>PRED_CAP_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cùng nhau góp vốn</t>
+          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cùng nhau góp vốn</t>
+          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng | cấp đăng ký doanh nghiệp theo quy trình dự phòng với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>cung_nhau_gop_von</t>
+          <t>cap_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>von_va_gop_von</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>công ty</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>dang_ky_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2888,51 +2928,55 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cung_nhau_gop_von</t>
+          <t>map_khi_thay_cum_cap_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PRED_NEU_CHUA_NHAN</t>
+          <t>PRED_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nếu chưa nhận</t>
+          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nếu chưa nhận</t>
+          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp | đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>neu_chua_nhan</t>
+          <t>dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>ten_doanh_nghiep</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2952,39 +2996,39 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PRED_XEM_XET_VA_CAP_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_NHAN_HO_SO_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh nhận hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp | xem xét và cấp Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>cấp tỉnh nhận hồ sơ đăng ký doanh nghiệp | cấp tỉnh nhận hồ sơ đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tham_dinh_ho_so</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>nhan_ho_so_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2994,17 +3038,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3019,44 +3063,44 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_nhan_ho_so_dang_ky_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PRED_NEU_CO_DU_DIEU_KIEN_QUY_DINH_TAI_KHOAN_1_DIEU_NAY_VA</t>
+          <t>PRED_CAP_THEO_SO_LUONG_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp.</t>
+          <t>cấp theo số lượng doanh nghiệp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp. với cơ quan đăng ký kinh doanh</t>
+          <t>cấp theo số lượng doanh nghiệp | cấp theo số lượng doanh nghiệp với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>cap_theo_so_luong_doanh_nghiep</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>hanh_dong_co_quan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3064,11 +3108,7 @@
           <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>cơ quan đăng ký kinh doanh</t>
@@ -3076,7 +3116,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3091,59 +3131,59 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_cap_theo_so_luong_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PRED_NEU_CO_DU_DIEU_KIEN_QUY_DINH_TAI_KHOAN_1_DIEU_NAY_VA</t>
+          <t>PRED_LAP_DIA_DIEM_KINH_DOANH_DEN_CO_QUAN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về</t>
+          <t>lập địa điểm kinh doanh đến Cơ quan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về | nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về với cơ quan đăng ký kinh doanh</t>
+          <t>lập địa điểm kinh doanh đến Cơ quan | lập địa điểm kinh doanh đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
+          <t>lap_dia_diem_kinh_doanh_den_co_quan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>chi_nhanh_van_phong_dai_dien</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>đăng ký kinh doanh cấp tỉnh nơi đặt địa điểm kinh doanh</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3168,39 +3208,39 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_thay_cum_lap_dia_diem_kinh_doanh_den_co_quan;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PRED_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_HOAT_DONG_CHI_NHANH</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp | Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh | cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3210,12 +3250,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>chi_nhanh</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3235,64 +3275,64 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_giay_chung_nhan_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PRED_THONG_BAO_BANG_VAN_BAN</t>
+          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA_CHO_NGU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh | thông báo bằng văn bản cho Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>thong_bao_bang_van_ban</t>
+          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>chậm nhất là 03 ngày làm việc trước ngày tạm ngừng kinh doanh hoặc tiếp tục kinh doanh trước thời hạn đã thông báo</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3312,54 +3352,54 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thong_bao_bang_van_ban;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PRED_GUI_HO_SO</t>
+          <t>PRED_DUNG_THUC_HIEN_THU_TUC_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh</t>
+          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh | gửi hồ sơ giải thể doanh nghiệp cho Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
+          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp | dừng thực hiện thủ tục đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>gui_ho_so</t>
+          <t>dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>người thành lập doanh nghiệp</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>thời hạn</t>
+          <t>hồ sơ đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3384,44 +3424,44 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_ho_so;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PRED_THU_HOI</t>
+          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp trong</t>
+          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3429,10 +3469,14 @@
           <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3452,50 +3496,54 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thu_hoi</t>
+          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PRED_CAP_DANG_KY_CO_TRACH_NHIEM_TICH_HOP</t>
+          <t>PRED_HO_SO_BAO_GOM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>cấp đăng ký có trách nhiệm tích hợp</t>
+          <t>hồ sơ bao gồm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>cấp đăng ký có trách nhiệm tích hợp | cấp đăng ký có trách nhiệm tích hợp với cơ quan đăng ký kinh doanh</t>
+          <t>hồ sơ bao gồm | hồ sơ bao gồm với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>cap_dang_ky_co_trach_nhiem_tich_hop</t>
+          <t>ho_so_bao_gom</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>công ty</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nội dung đăng ký doanh nghiệp</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3505,7 +3553,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3520,54 +3568,54 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_dang_ky_co_trach_nhiem_tich_hop</t>
+          <t>map_khi_thay_cum_ho_so_bao_gom;thuong_di_kem_thanh_phan_ho_so</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PRED_VA_CAC_CO_QUAN_KHAC_GAY_PHIEN_HA</t>
+          <t>PRED_CAC_GIAY_TO_SAU_DAY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà</t>
+          <t>các giấy tờ sau đây</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà | Cơ quan đăng ký kinh doanh và các cơ quan khác gây phiền hà với cơ quan đăng ký kinh doanh</t>
+          <t>các giấy tờ sau đây | các giấy tờ sau đây với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>va_cac_co_quan_khac_gay_phien_ha</t>
+          <t>cac_giay_to_sau_day</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>công ty</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>tổ chức</t>
+          <t>nội dung đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3577,7 +3625,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3592,39 +3640,39 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_va_cac_co_quan_khac_gay_phien_ha;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRED_CAP_LAI_CHO_TO_CHUC</t>
+          <t>PRED_GUI_GIAY_DE_NGHI_DANG_KY_THAY_DOI_VON_DAU_TU_DEN_CO_</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>cấp lại cho tổ chức</t>
+          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>cấp lại cho tổ chức | cấp lại cho tổ chức với cơ quan đăng ký kinh doanh</t>
+          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan | gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>cap_lai_cho_to_chuc</t>
+          <t>gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3632,10 +3680,14 @@
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>giấy đề nghị</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3660,39 +3712,39 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_lai_cho_to_chuc</t>
+          <t>map_khi_thay_cum_gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_TAI_LIEU_BANG_TIENG_NUOC_NGOAI</t>
+          <t>PRED_TRA_LE_PHI_DANG_KY_DOANH_NGHIEP_VA_PHI_CONG_BO_NOI_D</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kèm theo tài liệu bằng tiếng nước ngoài.</t>
+          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kèm theo tài liệu bằng tiếng nước ngoài.</t>
+          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cong_bo</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>kem_theo_tai_lieu_bang_tieng_nuoc_ngoai</t>
+          <t>tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cong_bo</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3702,7 +3754,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
+          <t>trường hợp doanh nghiệp cập nhật</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -3713,7 +3765,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3728,24 +3780,24 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_HO_SO</t>
+          <t>PRED_KEM_THEO_VAN_BAN_GIAI_TRINH_CUA_DOANH_NGHIEP_VE_LY_D</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kèm theo hồ sơ</t>
+          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kèm theo hồ sơ</t>
+          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận | kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3755,7 +3807,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>kem_theo_ho_so</t>
+          <t>kem_theo_van_ban_giai_trinh_cua_doanh_nghiep_ve_ly_do_dang_ky_thay_doi_va_duoc_co_quan_dang_ky_kinh_doanh_cap_tinh_chap_thuan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3770,10 +3822,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>nội dung đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>khong</t>
@@ -3796,52 +3852,56 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_kem_theo_ho_so;thuong_di_kem_thanh_phan_ho_so</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PRED_VAN_BAN_UY_QUYEN</t>
+          <t>PRED_GIAI_QUYET_THU_TUC_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh tiếp tục giải quyết thủ tục đăng ký doanh nghiệp với các</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Văn bản ủy quyền; Giấy đề nghị đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh tiếp tục giải quyết thủ tục đăng ký doanh nghiệp với các | cấp tỉnh tiếp tục giải quyết thủ tục đăng ký doanh nghiệp với các với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>van_ban_uy_quyen</t>
+          <t>giai_quyet_thu_tuc_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>hanh_dong_co_quan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>trường hợp quy định tại khoản 1 Điều này khi:</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>khong</t>
@@ -3849,7 +3909,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3864,59 +3924,59 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_giai_quyet_thu_tuc_dang_ky_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PRED_CAP_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CHI_NHANH</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>cấp đăng ký doanh nghiệp theo quy trình dự phòng | cấp đăng ký doanh nghiệp theo quy trình dự phòng với cơ quan đăng ký kinh doanh</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh | thực hiện thủ tục chấm dứt hoạt động chi nhánh với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>cap_dang_ky_doanh_nghiep</t>
+          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>chi_nhanh_van_phong_dai_dien</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>dang_ky_doanh_nghiep</t>
+          <t>thực hiện</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3931,56 +3991,64 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PRED_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CUA_TAT_CA_DIA_</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp | đăng ký thay đổi tên. Doanh nghiệp có tên vi phạm phải đăng ký thay đổi tên doanh nghiệp với cơ quan đăng ký kinh doanh</t>
+          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan | thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>dang_ky</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>dang_ky_doanh_nghiep</t>
+          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ten_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+          <t>chi_nhanh_van_phong_dai_dien</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>thực hiện</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4000,60 +4068,64 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dang_ky_doanh_nghiep;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PRED_NEU_CONG_TY</t>
+          <t>PRED_THONG_BAO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nếu công ty</t>
+          <t>thông báo phải có các giấy tờ quy định tại các điểm a, b và c khoản 2 Điều 55 Nghị định này</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nếu công ty</t>
+          <t>thông báo phải có các giấy tờ quy định tại các điểm a, b và c khoản 2 Điều 55 Nghị định này | thông báo phải có các giấy tờ quy định tại các điểm a, b và c khoản 2 Điều 55 Nghị định này với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>dieu_kien_ap_dung</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>neu_cong_ty</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>dieu_kien</t>
+          <t>nop_ho_so</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>công ty cổ phần</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>cổ đông sáng lập</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>nội dung đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4063,54 +4135,54 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>map_cho_ve_dieu_kien_ap_dung;uu_tien_giu_nguyen_ngu_canh</t>
+          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRED_LAP_DIA_DIEM_KINH_DOANH_DEN_CO_QUAN</t>
+          <t>PRED_THONG_BAO_CHO_CO_QUAN_QUAN_LY_THUE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>lập địa điểm kinh doanh đến Cơ quan</t>
+          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>lập địa điểm kinh doanh đến Cơ quan | lập địa điểm kinh doanh đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế | cấp tỉnh thông báo cho Cơ quan quản lý thuế với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>lap_dia_diem_kinh_doanh_den_co_quan</t>
+          <t>thong_bao_cho_co_quan_quan_ly_thue</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
+          <t>thong_bao</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>đăng ký kinh doanh cấp tỉnh nơi đặt địa điểm kinh doanh</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4135,44 +4207,44 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_lap_dia_diem_kinh_doanh_den_co_quan;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_thong_bao_cho_co_quan_quan_ly_thue;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PRED_CAP_GIAY_CHUNG_NHAN_DANG_KY_HOAT_DONG_CHI_NHANH</t>
+          <t>PRED_HUY_BO_QUYET_DINH_THU_HOI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
+          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi Giấy chứng nhận đăng ký doanh nghiệp đồng thời khôi phục Giấy chứng nhận đăng ký doanh nghiệp trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp trong các</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh | cấp tỉnh cấp Giấy chứng nhận đăng ký hoạt động chi nhánh với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi Giấy chứng nhận đăng ký doanh nghiệp đồng thời khôi phục Giấy chứng nhận đăng ký doanh nghiệp trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp trong các | cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi Giấy chứng nhận đăng ký doanh nghiệp đồng thời khôi phục Giấy chứng nhận đăng ký doanh nghiệp trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp trong các với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
+          <t>huy_bo_quyet_dinh_thu_hoi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4182,7 +4254,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>chi_nhanh</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4192,7 +4264,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4207,57 +4279,61 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_huy_bo_quyet_dinh_thu_hoi</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PRED_TIEP_NHAN_DE_NHAP_THONG_TIN_VAO_HE_THONG_THONG_TIN_Q</t>
+          <t>PRED_BAN_HANH_QUYET_DINH_THU_HOI_CHI_NHANH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tiếp nhận để nhập thông tin vào Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh ban hành quyết định thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>tiếp nhận để nhập thông tin vào Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh ban hành quyết định thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh | cấp tỉnh ban hành quyết định thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiep_nhan_ho_so</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>tiep_nhan_de_nhap_thong_tin_vao_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>ban_hanh_quyet_dinh_thu_hoi_chi_nhanh</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>hanh_dong_co_quan</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Hồ sơ đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>chi_nhanh</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>khong</t>
@@ -4270,7 +4346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4280,39 +4356,39 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_tiep_nhan_de_nhap_thong_tin_vao_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>map_khi_thay_cum_ban_hanh_quyet_dinh_thu_hoi_chi_nhanh;co_ngoai_le_can_xu_ly_rieng</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA_CHO_NGU</t>
+          <t>PRED_DANG_TAI_DANH_SACH_CHU_NO_TREN_CONG_THONG_TIN_QUOC_G</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ.</t>
+          <t>cấp tỉnh đăng tải danh sách chủ nợ trên Cổng thông tin quốc gia về đăng ký doanh nghiệp.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ. với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh đăng tải danh sách chủ nợ trên Cổng thông tin quốc gia về đăng ký doanh nghiệp. | cấp tỉnh đăng tải danh sách chủ nợ trên Cổng thông tin quốc gia về đăng ký doanh nghiệp. với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>dang_tai_danh_sach_chu_no_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4322,7 +4398,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
+          <t>tin quốc</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4332,7 +4408,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4347,29 +4423,29 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>map_khi_thay_cum_dang_tai_danh_sach_chu_no_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PRED_DUNG_THUC_HIEN_THU_TUC_DANG_KY_DOANH_NGHIEP</t>
+          <t>PRED_DANG_TAI_QUYET_DINH_TREN_CONG_THONG_TIN_QUOC_GIA_VE_</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp</t>
+          <t>cấp tỉnh đăng tải quyết định trên Cổng thông tin quốc gia về đăng ký doanh nghiệp và chuyển tình trạng pháp lý của doanh nghiệp sang tình trạng đã phá sản</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>dừng thực hiện thủ tục đăng ký doanh nghiệp | dừng thực hiện thủ tục đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh đăng tải quyết định trên Cổng thông tin quốc gia về đăng ký doanh nghiệp và chuyển tình trạng pháp lý của doanh nghiệp sang tình trạng đã phá sản | cấp tỉnh đăng tải quyết định trên Cổng thông tin quốc gia về đăng ký doanh nghiệp và chuyển tình trạng pháp lý của doanh nghiệp sang tình trạng đã phá sản với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4379,7 +4455,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep</t>
+          <t>dang_tai_quyet_dinh_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_chuyen_tinh_trang_phap_ly_cua_doanh_nghiep_sang_tinh_trang_da_pha_san</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4389,12 +4465,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>người thành lập doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>hồ sơ đăng ký doanh nghiệp</t>
+          <t>dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4419,29 +4495,29 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_dung_thuc_hien_thu_tuc_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_dang_tai_quyet_dinh_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_chuyen_tinh_trang_phap_ly_cua_doanh_nghiep_sang_tinh_trang_da_pha_san;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PRED_TRAO_GIAY_TIEP_NHAN_HO_SO_VA_HEN_TRA_KET_QUA</t>
+          <t>PRED_PHAT_HIEN_NOI_DUNG_THONG_TIN_DANG_KY_DOANH_NGHIEP_TR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả</t>
+          <t>cấp tỉnh phát hiện nội dung thông tin đăng ký doanh nghiệp trong Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp không có hoặc không chính xác so với hồ sơ bản giấy của doanh nghiệp do quá trình chuyển đổi dữ liệu vào Cơ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả | cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh phát hiện nội dung thông tin đăng ký doanh nghiệp trong Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp không có hoặc không chính xác so với hồ sơ bản giấy của doanh nghiệp do quá trình chuyển đổi dữ liệu vào Cơ | cấp tỉnh phát hiện nội dung thông tin đăng ký doanh nghiệp trong Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệp không có hoặc không chính xác so với hồ sơ bản giấy của doanh nghiệp do quá trình chuyển đổi dữ liệu vào Cơ với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4451,7 +4527,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua</t>
+          <t>phat_hien_noi_dung_thong_tin_dang_ky_doanh_nghiep_trong_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep_khong_co_hoac_khong_chinh_xac_so_voi_ho_so_ban_giay_cua_doanh_nghiep_do_qua_trinh_chuyen_doi_du_lieu_vao_co</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4466,7 +4542,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
+          <t>sở dữ liệu quốc gia về đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4496,49 +4572,49 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua;thuong_di_kem_thoi_han</t>
+          <t>map_khi_thay_cum_phat_hien_noi_dung_thong_tin_dang_ky_doanh_nghiep_trong_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghiep_khong_co_hoac_khong_chinh_xac_so_voi_ho_so_ban_giay_cua_doanh_nghiep_do_qua_trinh_chuyen_doi_du_lieu_vao_co;thuong_di_kem_thoi_han</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PRED_HO_SO_BAO_GOM</t>
+          <t>PRED_CAP_DANG_KY_THANH_LAP_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>hồ sơ bao gồm</t>
+          <t>cấp đăng ký thành lập doanh nghiệp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hồ sơ bao gồm | hồ sơ bao gồm với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp đăng ký thành lập doanh nghiệp | cấp đăng ký thành lập doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ho_so_bao_gom</t>
+          <t>cap_dang_ky_thanh_lap_doanh_nghiep</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4553,7 +4629,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4568,49 +4644,49 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_ho_so_bao_gom;thuong_di_kem_thanh_phan_ho_so</t>
+          <t>map_khi_thay_cum_cap_dang_ky_thanh_lap_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PRED_CAC_GIAY_TO_SAU_DAY</t>
+          <t>PRED_CHIA_SE_THONG_TIN_VE_GIAY_CHUNG_NHAN_DANG_KY_DOANH_N</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>các giấy tờ sau đây</t>
+          <t>cấp tỉnh chia sẻ thông tin về Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>các giấy tờ sau đây | các giấy tờ sau đây với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp tỉnh chia sẻ thông tin về Giấy chứng nhận đăng ký doanh nghiệp | cấp tỉnh chia sẻ thông tin về Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>cac_giay_to_sau_day</t>
+          <t>chia_se_thong_tin_ve_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>nop_ho_so</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>công ty</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4625,7 +4701,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4640,24 +4716,24 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_chia_se_thong_tin_ve_giay_chung_nhan_dang_ky_doanh_nghiep;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PRED_GUI_GIAY_DE_NGHI_DANG_KY_THAY_DOI_VON_DAU_TU_DEN_CO_</t>
+          <t>PRED_CAP_BAN_SAO_GIAY_CHUNG_NHAN_DANG_KY_DOANH_NGHIEP</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan</t>
+          <t>cấp bản sao Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan | gửi giấy đề nghị đăng ký thay đổi vốn đầu tư đến Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cấp bản sao Giấy chứng nhận đăng ký doanh nghiệp | cấp bản sao Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4667,7 +4743,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
+          <t>cap_ban_sao_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4675,14 +4751,10 @@
           <t>nop_ho_so</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>doanh nghiệp</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>giấy đề nghị</t>
+          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4712,52 +4784,56 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_gui_giay_de_nghi_dang_ky_thay_doi_von_dau_tu_den_co_quan</t>
+          <t>map_khi_thay_cum_cap_ban_sao_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PRED_TRA_LE_PHI_DANG_KY_DOANH_NGHIEP_VA_PHI_CONG_BO_NOI_D</t>
+          <t>PRED_CO_QUAN_DANG_KY_KINH_DOANH</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
+          <t>Cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>trả lệ phí đăng ký doanh nghiệp và phí công bố nội dung đăng ký doanh nghiệp trong</t>
+          <t>Cơ quan đăng ký kinh doanh | Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>cong_bo</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
+          <t>co_quan_dang_ky_kinh_doanh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>cong_bo</t>
+          <t>dang_ky</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>cấp xã và các cơ quan khác gây phiền hà đối với tổ chức</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>khong</t>
@@ -4780,24 +4856,24 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_tra_le_phi_dang_ky_doanh_nghiep_va_phi_cong_bo_noi_dung_dang_ky_doanh_nghiep_trong</t>
+          <t>map_khi_thay_cum_co_quan_dang_ky_kinh_doanh;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PRED_KEM_THEO_VAN_BAN_GIAI_TRINH_CUA_DOANH_NGHIEP_VE_LY_D</t>
+          <t>PRED_XA_TIEP_NHAN_HO_SO_DANG_KY_HO_KINH_DOANH_VAO_HE_THON</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận</t>
+          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận | kèm theo văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi và được Cơ quan đăng ký kinh doanh cấp tỉnh chấp thuận với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh | xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4807,7 +4883,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>kem_theo_van_ban_giai_trinh_cua_doanh_nghiep_ve_ly_do_dang_ky_thay_doi_va_duoc_co_quan_dang_ky_kinh_doanh_cap_tinh_chap_thuan</t>
+          <t>xa_tiep_nhan_ho_so_dang_ky_ho_kinh_doanh_vao_he_thong_thong_tin_ve_dang_ky_ho_kinh_doanh</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4817,17 +4893,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>doanh nghiệp</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>nội dung đăng ký doanh nghiệp</t>
+          <t>hồ sơ đáp ứng các điều kiện sau đây:</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4837,7 +4913,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4852,24 +4928,24 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>map_khi_noi_dung_la_thanh_phan_ho_so_hoac_giay_to_kem_theo</t>
+          <t>map_khi_thay_cum_xa_tiep_nhan_ho_so_dang_ky_ho_kinh_doanh_vao_he_thong_thong_tin_ve_dang_ky_ho_kinh_doanh</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CHI_NHANH</t>
+          <t>PRED_XA_TIEP_TUC_GIAI_QUYET_THU_TUC_DANG_KY_HO_KINH_DOANH</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan</t>
+          <t>xã tiếp tục giải quyết thủ tục đăng ký hộ kinh doanh cho hộ kinh doanh thuộc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan | thực hiện thủ tục chấm dứt hoạt động chi nhánh, văn phòng đại diện, địa điểm kinh doanh của doanh nghiệp tại Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>xã tiếp tục giải quyết thủ tục đăng ký hộ kinh doanh cho hộ kinh doanh thuộc | xã tiếp tục giải quyết thủ tục đăng ký hộ kinh doanh cho hộ kinh doanh thuộc với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4879,23 +4955,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
+          <t>xa_tiep_tuc_giai_quyet_thu_tuc_dang_ky_ho_kinh_doanh_cho_ho_kinh_doanh_thuoc</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>hanh_dong_co_quan</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>thực hiện</t>
+          <t>trường hợp quy định tại khoản 1 Điều này khi:</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4920,50 +5000,50 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_chi_nhanh</t>
+          <t>map_khi_thay_cum_xa_tiep_tuc_giai_quyet_thu_tuc_dang_ky_ho_kinh_doanh_cho_ho_kinh_doanh_thuoc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PRED_THUC_HIEN_THU_TUC_CHAM_DUT_HOAT_DONG_CUA_TAT_CA_DIA_</t>
+          <t>PRED_KHOI_PHUC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan</t>
+          <t>khôi phục lại Giấy chứng nhận đăng ký hộ kinh doanh sau</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan | thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>khôi phục lại Giấy chứng nhận đăng ký hộ kinh doanh sau | khôi phục lại Giấy chứng nhận đăng ký hộ kinh doanh sau với cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
+          <t>khoi_phuc</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>chi_nhanh_van_phong_dai_dien</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>thực hiện</t>
-        </is>
-      </c>
+          <t>thu_hoi</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4988,59 +5068,55 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan</t>
+          <t>map_khi_thay_cum_khoi_phuc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PRED_THONG_BAO_CHO_CO_QUAN_QUAN_LY_THUE</t>
+          <t>PRED_TRA_CUU_THONG_TIN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế</t>
+          <t>tra cứu thông tin đăng ký hộ kinh doanh miễn phí trên Cổng thông tin quốc gia về đăng ký doanh nghiệp tại địa chỉ www.dangkykinhdoanh.gov.vn</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>cấp tỉnh thông báo cho Cơ quan quản lý thuế | cấp tỉnh thông báo cho Cơ quan quản lý thuế với cơ quan đăng ký kinh doanh cấp tỉnh</t>
+          <t>tra cứu thông tin đăng ký hộ kinh doanh miễn phí trên Cổng thông tin quốc gia về đăng ký doanh nghiệp tại địa chỉ www.dangkykinhdoanh.gov.vn</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>cong_bo</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>thong_bao_cho_co_quan_quan_ly_thue</t>
+          <t>tra_cuu_thong_tin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>thong_bao</t>
+          <t>cong_bo</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>cơ quan đăng ký kinh doanh</t>
+          <t>doanh nghiệp</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
+          <t>dang_ky_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5060,223 +5136,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>map_khi_thay_cum_thong_bao_cho_co_quan_quan_ly_thue;khong_dong_nhat_voi_cong_bo;thuong_di_kem_thoi_han</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>PRED_HUY_BO_QUYET_DINH_THU_HOI</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp | cấp tỉnh ra quyết định hủy bỏ quyết định thu hồi và khôi phục Giấy chứng nhận đăng ký doanh nghiệp với cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>huy_bo_quyet_dinh_thu_hoi</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Giấy chứng nhận đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh cấp tỉnh</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_huy_bo_quyet_dinh_thu_hoi;thuong_di_kem_thoi_han</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>PRED_CO_QUAN_DANG_KY_KINH_DOANH</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Cơ quan đăng ký kinh doanh | Cơ quan đăng ký kinh doanh với cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>dang_ky</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>co_quan_dang_ky_kinh_doanh</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>dang_ky</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>cấp xã và các cơ quan khác gây phiền hà đối với tổ chức</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_co_quan_dang_ky_kinh_doanh;uu_tien_cho_hanh_vi_dang_ky_noi_dung_phap_ly</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>PRED_XA_TIEP_NHAN_HO_SO_DANG_KY_HO_KINH_DOANH_VAO_HE_THON</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh | xã tiếp nhận hồ sơ đăng ký hộ kinh doanh vào Hệ thống thông tin về đăng ký hộ kinh doanh với cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>xa_tiep_nhan_ho_so_dang_ky_ho_kinh_doanh_vao_he_thong_thong_tin_ve_dang_ky_ho_kinh_doanh</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>nop_ho_so</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>hồ sơ đáp ứng các điều kiện sau đây:</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>cơ quan đăng ký kinh doanh</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>map_khi_thay_cum_xa_tiep_nhan_ho_so_dang_ky_ho_kinh_doanh_vao_he_thong_thong_tin_ve_dang_ky_ho_kinh_doanh</t>
+          <t>map_khi_thay_cum_tra_cuu_thong_tin</t>
         </is>
       </c>
     </row>
